--- a/www/download/IND.value.m.mv.WIOD13.xlsx
+++ b/www/download/IND.value.m.mv.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1084201.07544688</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1017336.94224825</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1013030.7335603</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136662.86297132</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1199201.31919617</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192454.70086378</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1236532.21991013</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1173020.55792384</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>958118.362936836</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>884302.685700112</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>808630.932276116</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775290.998030032</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681479.539382944</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>641751.841410673</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>669699.35407042</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>999122.899954517</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1065198.23579569</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1088804.29647708</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>1107493.37981094</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1161364.30615776</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1305617.84261956</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1296974.19821357</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1180008.32452639</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>997741.792164231</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>894626.613179597</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>846902.900780348</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830011.889105936</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>721615.798182533</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>569839.811784431</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>562242.070681744</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>857413.069534259</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850907.426207846</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>897014.076328498</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>897558.806632495</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>960709.209402664</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>1038282.02387961</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026296.90289345</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>968692.287226128</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872418.557470349</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>805883.96767791</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>771508.442178694</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739599.393276983</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659558.711576959</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>678557.13892158</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>617645.82888524</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.228</t>
+          <t>9226911.70378469</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.764</t>
+          <t>8764119.64146087</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.205</t>
+          <t>10204599.9994941</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9149756.22580577</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.239</t>
+          <t>8377412.12839312</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.843</t>
+          <t>7842579.27736725</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.002</t>
+          <t>7001092.33543368</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.114</t>
+          <t>6112807.48315124</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.631</t>
+          <t>4631224.07669877</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.939</t>
+          <t>3938633.16536029</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3660026.21433966</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.308</t>
+          <t>3307417.53937873</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.665</t>
+          <t>2664332.63343126</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.289</t>
+          <t>2289177.44885155</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2434879.98010094</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.082</t>
+          <t>4081623.42722757</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.814</t>
+          <t>3813992.61202764</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.699</t>
+          <t>3698428.74488542</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.779</t>
+          <t>3778732.66033455</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.422</t>
+          <t>5551082.61931468</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.847</t>
+          <t>4847056.5388314</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5456374.56697031</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.908</t>
+          <t>5907313.26189077</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.441</t>
+          <t>5440627.15969204</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.777</t>
+          <t>4777261.16300606</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.926</t>
+          <t>3925848.76621235</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.306</t>
+          <t>3305921.47021085</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.703</t>
+          <t>2702807.63164256</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>2273525.24560369</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.382</t>
+          <t>2381882.38334501</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1176373.92397615</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132393.14631705</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1090440.06841863</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1152514.58031605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.128</t>
+          <t>1166976.63388251</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1090343.00339824</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1168968.72218828</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1072791.38499064</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>970985.914295459</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>936215.132744313</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>901572.914845827</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>831641.07350269</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732285.777300302</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>695019.65889171</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>711359.092413684</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24569235.1275882</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21618703.1855218</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.591</t>
+          <t>19589964.6387571</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18.578</t>
+          <t>18578293.1583089</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>17585620.5272961</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>15185975.8143618</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13.977</t>
+          <t>13975545.3251904</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.958</t>
+          <t>12956638.9084832</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12209822.2597021</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11119667.6379332</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.921</t>
+          <t>9920870.0756531</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.612</t>
+          <t>8611456.91459338</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6.968</t>
+          <t>6967911.59831604</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5.607</t>
+          <t>5606705.55264043</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5.332</t>
+          <t>5331395.87745202</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>2014593.62749617</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.074</t>
+          <t>2073405.15530827</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.028</t>
+          <t>2027558.64583715</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2003178.0119987</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2326219.28211236</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2280179.27437245</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>2333241.01541893</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.137</t>
+          <t>2136637.20843423</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1855338.57911541</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1619600.01178018</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325511.54551017</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.241</t>
+          <t>1241253.66223678</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1021245.85170978</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192558.10858618</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829113.640695164</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>3470455.04774819</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3229520.11654104</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.522</t>
+          <t>3522017.243147</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>3221969.80487901</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.259</t>
+          <t>3280199.16645555</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>3224787.23627119</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3001447.66521143</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.592</t>
+          <t>2591182.43606391</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2103235.98831011</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1762484.98245971</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1621486.64863158</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1478915.08800615</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1235248.8078125</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>971359.84774349</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1036572.54416026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>840425.233029349</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>815378.698599823</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875528.296691493</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>897074.143825248</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>950069.441883344</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077030.33317684</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>1039220.95667235</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>977630.957394904</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.868</t>
+          <t>867254.083407612</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>814148.478006728</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>788868.364116852</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768044.381792033</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>689776.649254833</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542819.532647508</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553561.414810107</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>935994.677743533</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>917055.131404494</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1056197.59564336</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>969507.97096288</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>935742.07423448</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>970879.504975657</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1008600.20808726</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>916666.173190581</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814971.708002424</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>747763.624019737</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>698075.357312235</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>639881.197547818</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563977.35609492</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476674.788117912</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>481040.474101487</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1078529.2307815</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1056429.40157442</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1121092.24807755</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150027.25147584</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.249</t>
+          <t>1272401.96177118</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1398904.87244198</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1344188.64155524</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1239346.32887107</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1014104.05968544</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>911560.937269192</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>862903.742580055</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>822641.961652903</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>728108.618166198</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601760.961309017</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>556642.209775234</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>6341849.4716636</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>5240079.99986205</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.365</t>
+          <t>5364297.80524225</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.489</t>
+          <t>4488653.56372391</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4148846.41557092</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4191576.39662423</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>4095587.58329891</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.638</t>
+          <t>3637257.06777023</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2965715.52171097</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>2644320.6812522</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2182875.4981895</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>1892391.59245988</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1453884.44129711</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1285085.59547857</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1373274.72572533</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>985569.067408047</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>981621.815887496</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>997792.005803129</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1030991.14051737</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1137946.70290482</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1171292.94817361</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1115607.97308408</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1044406.30473641</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>931748.862705249</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815563.920433767</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>796234.970319203</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754180.616008507</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636060.337128153</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>532685.543701311</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491404.051209114</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>831421.648204105</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827310.833692886</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>834799.719726312</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>839794.844323164</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>885588.06426118</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955213.352540753</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>949501.923678553</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>885247.382852885</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762608.531654192</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693944.9006184</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>670749.519372522</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634253.162430494</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>561849.901911795</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>462920.995613276</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440971.920880736</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1037292.91374497</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1013233.16426258</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912096.556863017</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>879231.976478597</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>898758.020598977</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>901937.397670404</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>914117.702993001</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>837747.205511359</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754358.128247717</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>667820.002178845</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630953.743786967</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>593079.276231948</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>521725.789267342</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>477353.796875242</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529508.885527107</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>1828947.86770657</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>1813590.34229402</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>1871292.50699954</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1929859.4141935</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>1911217.30032026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2220631.13128723</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2029538.68987665</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.824</t>
+          <t>1823630.97122267</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1450475.25489957</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1260414.06814378</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1166918.75142489</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159259.15558521</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1024005.74735153</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893806.201668051</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>942723.375897933</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.992</t>
+          <t>3991642.79066251</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3835957.99116198</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3716946.05788604</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.732</t>
+          <t>3731906.79682199</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>4036911.10074108</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.997</t>
+          <t>3996846.32116389</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>3431719.71396624</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.972</t>
+          <t>2971174.73570774</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.425</t>
+          <t>2424795.10984136</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1882203.30140102</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1747536.14673014</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.657</t>
+          <t>1656619.35765795</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1415107.91127874</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1044689.34800763</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1238578.33329074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11.139</t>
+          <t>11138483.6395895</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.042</t>
+          <t>10041564.6983301</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.708</t>
+          <t>9708160.44058072</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24.027</t>
+          <t>24026978.7208177</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.295</t>
+          <t>16446226.9145042</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14.388</t>
+          <t>14387913.6195075</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14.907</t>
+          <t>14906893.8060538</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13.197</t>
+          <t>13196956.2471498</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11.281</t>
+          <t>11280665.2988464</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11.189</t>
+          <t>11189438.049628</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9.403</t>
+          <t>9402907.64028565</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6.676</t>
+          <t>6675671.26484329</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>5.667</t>
+          <t>5666768.94375878</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4929867.78644239</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.892</t>
+          <t>4891530.39405264</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30.349</t>
+          <t>30346716.5985353</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>29758799.0380364</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.768</t>
+          <t>27766702.9590914</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27.477</t>
+          <t>27477328.1510127</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26.564</t>
+          <t>27397981.0501625</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27378565.1532323</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.949</t>
+          <t>28944869.3030036</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28.179</t>
+          <t>28175518.2723661</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25.978</t>
+          <t>25976861.6827824</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23.295</t>
+          <t>23295085.7539089</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>20.321</t>
+          <t>20320410.8010739</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>17789205.5615929</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>13.861</t>
+          <t>13860056.4312944</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>13.179</t>
+          <t>13178102.3259055</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>13.389</t>
+          <t>13388805.7994188</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1176402.51599648</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1116418.62599623</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1040794.9912629</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1011697.74055687</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>1051436.57231408</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1083676.66739158</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>1046951.16770044</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>929509.061000326</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>770351.846906812</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>713386.703744335</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>682891.516163814</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>621548.028134913</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580512.22264715</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>525000.66253043</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>578085.361509632</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1104961.64170619</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.023</t>
+          <t>1022298.16335471</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1017620.82149554</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1032669.79784567</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1092802.91662145</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.199</t>
+          <t>1199003.62378247</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1190503.45272131</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1113137.69503714</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955913.91824069</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870693.074271715</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825970.528527417</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829146.128551061</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>722149.970954244</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>577690.937128957</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571125.652195815</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>925897.816668089</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1007709.87483224</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1059977.82943763</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1069946.77071074</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1011884.74980592</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>984715.167468202</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1097864.27148411</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1107720.82986444</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1061466.66146328</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1012486.26459761</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1001115.52612843</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.051</t>
+          <t>1052564.48415595</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>997884.095662953</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>899162.46738812</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>831136.553838476</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>2834390.91948254</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.645</t>
+          <t>2644671.02365652</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>2777721.93042901</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.273</t>
+          <t>3273374.23602873</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>2981393.20360304</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>2763364.68705036</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>2943038.18430007</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>2705740.23898546</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.503</t>
+          <t>2503124.63497982</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>2297935.57842268</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>1911106.54918065</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>1747138.24467854</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1556233.05213108</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1559943.85736557</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.651</t>
+          <t>1650828.67454238</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>7603710.79714579</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>6138667.72494581</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.168</t>
+          <t>5167563.26184536</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.824</t>
+          <t>4823307.18685756</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.984</t>
+          <t>5026410.42769823</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.799</t>
+          <t>4799113.66327292</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.404</t>
+          <t>4403837.2841795</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>3918609.10464273</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3181117.85545952</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2459903.16572161</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2.233</t>
+          <t>2232275.00548145</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1944794.17260413</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1594542.11838766</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1350302.16694283</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1570244.63702763</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732221.98245345</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>662144.560487454</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>653078.933362048</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>677040.907127313</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>682145.671472575</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>750051.623621693</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>694452.598072937</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642072.557988281</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>589619.614572292</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545482.601857641</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542980.546251874</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516650.736114871</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423489.594658026</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374352.636673511</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423701.055412926</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>6238597.72654756</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>5226573.59507603</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4.565</t>
+          <t>4565066.80132117</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.329</t>
+          <t>4329204.96026438</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>4547061.16785443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.859</t>
+          <t>3858229.06883651</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.413</t>
+          <t>3411783.57450812</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3319195.72626271</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2800337.86972782</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>2347841.42236302</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2.124</t>
+          <t>2123674.21805567</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1739935.52495033</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1390102.41969116</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136542.39630996</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1157999.19046919</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4.361</t>
+          <t>4360767.37490472</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.905</t>
+          <t>3904881.98743669</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.285</t>
+          <t>3285135.3648874</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>3278119.5799271</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.105</t>
+          <t>3170341.93885454</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.804</t>
+          <t>2803577.64530086</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>2740459.17805726</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>2635976.25374579</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>2768453.83562918</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2709818.34736055</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2434953.71646214</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.207</t>
+          <t>2206726.0839569</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2028566.06615233</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2059616.78209007</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.488</t>
+          <t>2487825.11880041</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>1806604.02077174</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1787356.96514213</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.642</t>
+          <t>1641877.02789732</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1635404.13646905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1808675.93603383</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1877753.84941141</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>1712356.18089929</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1666960.2045624</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1418764.38664817</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1272774.0608792</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1092940.89734785</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1218997.90306884</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1003674.31489507</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898559.841125864</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>934937.96051092</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1058306.19940773</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1086642.61387565</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1108599.36313414</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1183618.01786448</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1264362.31720663</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>1289432.67418752</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1279843.35495211</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1081488.50649729</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018238.68045488</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>928458.002573144</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898634.397180354</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>835190.038269861</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>744869.945660585</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>640798.925233389</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649509.220687297</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4.175</t>
+          <t>4174911.58533731</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.855</t>
+          <t>3854616.35307047</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3835486.05213617</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.607</t>
+          <t>3607083.98400644</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.749</t>
+          <t>3806442.31905864</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.603</t>
+          <t>3603240.64113727</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.056</t>
+          <t>3055996.51582546</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.803</t>
+          <t>2802167.38284346</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2503880.25458019</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2109231.52806991</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1888539.21621569</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1714694.21836469</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1458266.57786851</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1150929.03272628</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343732.00912232</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>1995340.48794038</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1881819.10231743</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.902</t>
+          <t>1901404.08622874</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.937</t>
+          <t>1936810.24763107</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>2001275.19404037</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2182974.43005058</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>2172390.41988692</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>1995555.15821174</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.662</t>
+          <t>1661696.71138193</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1476030.21106481</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1388920.15201567</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1271128.93472734</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1125998.66092998</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1043309.77516129</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>936824.082736531</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9.767</t>
+          <t>9766449.18109688</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.326</t>
+          <t>9325732.77799318</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.067</t>
+          <t>9067101.0872616</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>8.147</t>
+          <t>8147526.32733111</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.194</t>
+          <t>10411695.4362851</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9.504</t>
+          <t>9503841.55375746</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8.381</t>
+          <t>8380055.86663338</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7.212</t>
+          <t>7211006.81922847</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.678</t>
+          <t>5677578.18784656</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4.209</t>
+          <t>4209105.16199111</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>3439152.1802336</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>2917235.04468153</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2.194</t>
+          <t>2193837.16675333</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>1841840.90633039</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>2214503.23103496</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10.285</t>
+          <t>10284198.1763382</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.987</t>
+          <t>7986952.9234165</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.424</t>
+          <t>7423506.7301785</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.218</t>
+          <t>9218178.78490045</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.942</t>
+          <t>15136535.3226367</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12.045</t>
+          <t>12045216.7532612</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.178</t>
+          <t>10176648.2351402</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9.077</t>
+          <t>9075778.61308029</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.693</t>
+          <t>7693239.50002815</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5.699</t>
+          <t>5699220.70314062</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.655</t>
+          <t>4655201.52605941</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.624</t>
+          <t>3623599.47801161</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.871</t>
+          <t>2870710.08486619</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294330.8491474</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2931183.96291603</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4.171</t>
+          <t>4170198.80377587</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>3924428.12237528</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3674162.56737825</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3.393</t>
+          <t>3392514.12852758</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.718</t>
+          <t>3794863.09771634</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.568</t>
+          <t>3568096.61812316</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3379013.3136871</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.852</t>
+          <t>2851656.39370248</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2211136.40632995</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.926</t>
+          <t>1926233.10958053</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>1821115.76918841</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.661</t>
+          <t>1660970.21023638</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1378458.57611705</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>1516976.93800301</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1699103.30592107</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2.163</t>
+          <t>2162303.80289559</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2103600.45754184</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.032</t>
+          <t>2031283.10624601</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>2004444.73486272</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>2136265.63313245</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2221237.38726426</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.218</t>
+          <t>2218262.01063322</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.026</t>
+          <t>2026225.15203071</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1803420.23141714</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>1544366.79377452</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1433731.15757492</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1348852.70912006</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1122906.39970986</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077568.7797512</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1118461.80901041</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>972452.572007855</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>862042.698364441</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>886660.217348328</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>918917.46915329</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>964097.607887584</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.996</t>
+          <t>995797.130564032</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012055.64038004</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>915244.475825327</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>798127.554558003</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>710657.313746211</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695456.098710084</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642031.07989784</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>573495.029175092</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473165.481453209</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>470840.068880769</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.388</t>
+          <t>3387448.71001925</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.275</t>
+          <t>3275086.71798951</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3229237.66767781</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3.138</t>
+          <t>3137823.9597182</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3465107.09788914</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3176203.87932751</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>3985032.53755914</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3.591</t>
+          <t>3590030.35587609</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.818</t>
+          <t>2817886.46107436</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2389873.1171787</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2039428.01014171</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.885</t>
+          <t>1885083.31766517</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1556825.70770513</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1385458.44155167</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1511835.67046093</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>2586911.52903202</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>2475233.12772919</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.411</t>
+          <t>2410591.97658536</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2630331.95885519</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>2528450.16695349</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2488358.07840255</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2627367.86345774</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t>2685724.78415051</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.618</t>
+          <t>2617663.0736036</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>2522282.78291038</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>2300416.75510648</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>2198150.44520929</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>2052834.64057969</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1939269.49712488</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.903</t>
+          <t>1903001.96416245</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1081782.69590976</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1027792.15857264</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988631.204569577</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>978406.191077378</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>1012804.94968883</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>990955.235517313</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>953368.420469671</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>932890.298627475</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893755.783190072</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870529.290933405</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>847342.252199464</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814564.583637271</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>741719.368356281</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>702478.170124608</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>675721.976499123</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>8.352</t>
+          <t>8351783.98777469</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.258</t>
+          <t>8257976.69214431</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.372</t>
+          <t>8371463.06945923</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>8.817</t>
+          <t>8816836.81974511</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8.871</t>
+          <t>9057241.78749677</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9.005</t>
+          <t>9004477.73292828</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9519445.62438155</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9.562</t>
+          <t>9561476.69128052</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>9.099</t>
+          <t>9099054.27192026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.439</t>
+          <t>8438951.55716153</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>7.673</t>
+          <t>7672688.92072473</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>7.013</t>
+          <t>7012785.34999325</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6.115</t>
+          <t>6114368.18273704</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>5218218.46549991</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5.726</t>
+          <t>5726065.56316937</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>183.634</t>
+          <t>183612445.569038</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>169.453</t>
+          <t>169439243.842853</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>163.507</t>
+          <t>163493728.729652</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>175.551</t>
+          <t>175550771.404671</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>174.969</t>
+          <t>178581767.753414</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>167.859</t>
+          <t>167847384.853417</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>164.303</t>
+          <t>164277045.14863</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>152572839.802908</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>134.137</t>
+          <t>134127898.672181</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>118.719</t>
+          <t>118716199.868045</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>104.984</t>
+          <t>104979327.91457</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>92.312</t>
+          <t>92308522.2721742</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>76.749</t>
+          <t>76739252.6717971</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>68.015</t>
+          <t>68009778.5398627</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>70.852</t>
+          <t>70849499.4254023</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
